--- a/artfynd/A 60246-2023 artfynd.xlsx
+++ b/artfynd/A 60246-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,6 +1043,377 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Litslena</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114950410</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57764</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528252</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6485155</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Litslena</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114950079</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>burg, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>528170</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6485252</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Litslena</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114950078</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>burg, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528113</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6485180</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Rejlers - NVI Ljungsbro-Litslena</t>
         </is>
